--- a/Excel/BabelAtrConfig.xlsx
+++ b/Excel/BabelAtrConfig.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
   <si>
     <t>#</t>
   </si>
@@ -108,6 +108,9 @@
   </si>
   <si>
     <t>攻击</t>
+  </si>
+  <si>
+    <t>通天增伤</t>
   </si>
   <si>
     <t>生命加成</t>
@@ -1109,7 +1112,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1273,19 +1276,19 @@
         <v>4</v>
       </c>
       <c r="D9" s="1">
-        <v>201</v>
+        <v>1</v>
       </c>
       <c r="E9" s="1">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F9" s="1">
         <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>1001</v>
+        <v>96</v>
       </c>
       <c r="H9" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>16</v>
@@ -1305,10 +1308,10 @@
         <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="H10" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>17</v>
@@ -1328,7 +1331,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="H11" s="1">
         <v>1</v>
@@ -1342,7 +1345,7 @@
         <v>7</v>
       </c>
       <c r="D12" s="1">
-        <v>401</v>
+        <v>201</v>
       </c>
       <c r="E12" s="1">
         <v>5</v>
@@ -1351,16 +1354,16 @@
         <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>2001</v>
+        <v>1003</v>
       </c>
       <c r="H12" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="3:9">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1374,16 +1377,16 @@
         <v>1</v>
       </c>
       <c r="G13" s="1">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H13" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:9">
+    <row r="14" customHeight="1" spans="3:9">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1397,7 +1400,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="1">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="H14" s="1">
         <v>1</v>
@@ -1406,48 +1409,48 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A27" s="1" t="s">
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:9">
+      <c r="C15" s="1">
+        <v>10</v>
+      </c>
+      <c r="D15" s="1">
+        <v>401</v>
+      </c>
+      <c r="E15" s="1">
+        <v>5</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1">
+        <v>2003</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A28" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B28" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="I27" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="1:9">
-      <c r="C28" s="1">
-        <v>101</v>
-      </c>
-      <c r="D28" s="1">
-        <v>200</v>
-      </c>
-      <c r="E28" s="1">
-        <v>0</v>
-      </c>
-      <c r="F28" s="1">
-        <v>2</v>
-      </c>
-      <c r="G28" s="1">
-        <v>11</v>
-      </c>
-      <c r="H28" s="1">
-        <v>5</v>
-      </c>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
       <c r="I28" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="1:9">
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C29" s="1">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D29" s="1">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="E29" s="1">
         <v>0</v>
@@ -1456,10 +1459,10 @@
         <v>2</v>
       </c>
       <c r="G29" s="1">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H29" s="1">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>24</v>
@@ -1467,10 +1470,10 @@
     </row>
     <row r="30" customHeight="1" spans="1:9">
       <c r="C30" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D30" s="1">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="E30" s="1">
         <v>0</v>
@@ -1479,10 +1482,10 @@
         <v>2</v>
       </c>
       <c r="G30" s="1">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H30" s="1">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>25</v>
@@ -1490,10 +1493,10 @@
     </row>
     <row r="31" customHeight="1" spans="1:9">
       <c r="C31" s="1">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D31" s="1">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="E31" s="1">
         <v>0</v>
@@ -1502,13 +1505,36 @@
         <v>2</v>
       </c>
       <c r="G31" s="1">
-        <v>10003</v>
+        <v>12</v>
       </c>
       <c r="H31" s="1">
         <v>5</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="1:9">
+      <c r="C32" s="1">
+        <v>104</v>
+      </c>
+      <c r="D32" s="1">
+        <v>800</v>
+      </c>
+      <c r="E32" s="1">
+        <v>0</v>
+      </c>
+      <c r="F32" s="1">
+        <v>2</v>
+      </c>
+      <c r="G32" s="1">
+        <v>10003</v>
+      </c>
+      <c r="H32" s="1">
+        <v>5</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/BabelAtrConfig.xlsx
+++ b/Excel/BabelAtrConfig.xlsx
@@ -134,16 +134,16 @@
     <t>特殊奖励，只有此等级奖励一次，不会增加</t>
   </si>
   <si>
+    <t>冷却</t>
+  </si>
+  <si>
     <t>攻速</t>
   </si>
   <si>
+    <t>移动速度</t>
+  </si>
+  <si>
     <t>爆伤</t>
-  </si>
-  <si>
-    <t>移速</t>
-  </si>
-  <si>
-    <t>攻击倍率</t>
   </si>
 </sst>
 </file>
@@ -1299,7 +1299,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="1">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="E10" s="1">
         <v>5</v>
@@ -1345,7 +1345,7 @@
         <v>7</v>
       </c>
       <c r="D12" s="1">
-        <v>201</v>
+        <v>301</v>
       </c>
       <c r="E12" s="1">
         <v>5</v>
@@ -1391,7 +1391,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="1">
-        <v>401</v>
+        <v>501</v>
       </c>
       <c r="E14" s="1">
         <v>5</v>
@@ -1414,7 +1414,7 @@
         <v>10</v>
       </c>
       <c r="D15" s="1">
-        <v>401</v>
+        <v>601</v>
       </c>
       <c r="E15" s="1">
         <v>5</v>
@@ -1459,7 +1459,7 @@
         <v>2</v>
       </c>
       <c r="G29" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H29" s="1">
         <v>5</v>
@@ -1482,10 +1482,10 @@
         <v>2</v>
       </c>
       <c r="G30" s="1">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H30" s="1">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>25</v>
@@ -1508,7 +1508,7 @@
         <v>12</v>
       </c>
       <c r="H31" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>26</v>
@@ -1528,10 +1528,10 @@
         <v>2</v>
       </c>
       <c r="G32" s="1">
-        <v>10003</v>
+        <v>22</v>
       </c>
       <c r="H32" s="1">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>27</v>

--- a/Excel/BabelAtrConfig.xlsx
+++ b/Excel/BabelAtrConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -140,7 +145,7 @@
     <t>攻速</t>
   </si>
   <si>
-    <t>移动速度</t>
+    <t>暴击</t>
   </si>
   <si>
     <t>爆伤</t>
@@ -1450,7 +1455,7 @@
         <v>101</v>
       </c>
       <c r="D29" s="1">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E29" s="1">
         <v>0</v>
@@ -1473,7 +1478,7 @@
         <v>102</v>
       </c>
       <c r="D30" s="1">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E30" s="1">
         <v>0</v>
@@ -1496,7 +1501,7 @@
         <v>103</v>
       </c>
       <c r="D31" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="E31" s="1">
         <v>0</v>
@@ -1505,10 +1510,10 @@
         <v>2</v>
       </c>
       <c r="G31" s="1">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="H31" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>26</v>
@@ -1519,7 +1524,7 @@
         <v>104</v>
       </c>
       <c r="D32" s="1">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="E32" s="1">
         <v>0</v>

--- a/Excel/BabelAtrConfig.xlsx
+++ b/Excel/BabelAtrConfig.xlsx
@@ -1215,7 +1215,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
@@ -1238,7 +1238,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F7" s="1">
         <v>1</v>
@@ -1261,7 +1261,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F8" s="1">
         <v>1</v>
@@ -1284,7 +1284,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F9" s="1">
         <v>1</v>
@@ -1307,7 +1307,7 @@
         <v>101</v>
       </c>
       <c r="E10" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F10" s="1">
         <v>1</v>
@@ -1330,7 +1330,7 @@
         <v>201</v>
       </c>
       <c r="E11" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F11" s="1">
         <v>1</v>
@@ -1353,7 +1353,7 @@
         <v>301</v>
       </c>
       <c r="E12" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F12" s="1">
         <v>1</v>
@@ -1376,7 +1376,7 @@
         <v>401</v>
       </c>
       <c r="E13" s="1">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F13" s="1">
         <v>1</v>
@@ -1399,7 +1399,7 @@
         <v>501</v>
       </c>
       <c r="E14" s="1">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F14" s="1">
         <v>1</v>
@@ -1422,7 +1422,7 @@
         <v>601</v>
       </c>
       <c r="E15" s="1">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F15" s="1">
         <v>1</v>

--- a/Excel/BabelAtrConfig.xlsx
+++ b/Excel/BabelAtrConfig.xlsx
@@ -1212,10 +1212,10 @@
         <v>1</v>
       </c>
       <c r="D6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
@@ -1235,10 +1235,10 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F7" s="1">
         <v>1</v>
@@ -1258,10 +1258,10 @@
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F8" s="1">
         <v>1</v>
@@ -1281,10 +1281,10 @@
         <v>4</v>
       </c>
       <c r="D9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F9" s="1">
         <v>1</v>
@@ -1304,10 +1304,10 @@
         <v>5</v>
       </c>
       <c r="D10" s="1">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E10" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F10" s="1">
         <v>1</v>
@@ -1327,10 +1327,10 @@
         <v>6</v>
       </c>
       <c r="D11" s="1">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E11" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F11" s="1">
         <v>1</v>
@@ -1350,10 +1350,10 @@
         <v>7</v>
       </c>
       <c r="D12" s="1">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E12" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F12" s="1">
         <v>1</v>
@@ -1373,10 +1373,10 @@
         <v>8</v>
       </c>
       <c r="D13" s="1">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E13" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F13" s="1">
         <v>1</v>
@@ -1396,10 +1396,10 @@
         <v>9</v>
       </c>
       <c r="D14" s="1">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E14" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F14" s="1">
         <v>1</v>
@@ -1419,10 +1419,10 @@
         <v>10</v>
       </c>
       <c r="D15" s="1">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E15" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F15" s="1">
         <v>1</v>
